--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -14255,7 +14255,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>ad,had,head,heard,shared,trashed,thrashed</t>
+          <t>ad,had,hard,heard,shared,trashed,thrashed</t>
         </is>
       </c>
       <c r="L323">

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L326"/>
+  <dimension ref="A1:L338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14386,6 +14386,306 @@
         <v/>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>barked</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>bar,bear,bread,barked</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>rot</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>smoother</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>rot,sort,short,others,mothers,smoother</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>medication</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>me,men,mine,anime,median,mediant,dominate,mediation,medication</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>at,tan,tank,thank</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>sate</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>masteries</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>sate,stare,stream,steamer,steamers,masteries</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>lee</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>reclaimed</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>3</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>lee,leer,elder,dealer,emerald,remedial,reclaimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>widen</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>in,win,wind,widen</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ear</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>lateral</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>ear,real,alter,taller,lateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>flustering</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>is,sin,sing,sting,string,rusting,rustling,resulting,flustering</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>heart</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>he,the,heat,heart</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>sneaky</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>as,sea,sake,snake,sneaky</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ma</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>inflame</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>ma,man,main,anime,famine,inflame</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
